--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run9/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run9/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,784 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9285,0.0183,0.0012,0.0200</t>
-  </si>
-  <si>
-    <t>0.0200,0.0074,0.0024,0.9884</t>
-  </si>
-  <si>
-    <t>0.8960,0.0024,0.0025,0.1625</t>
-  </si>
-  <si>
-    <t>0.0387,0.0016,0.0004,0.9856</t>
-  </si>
-  <si>
-    <t>0.9973,0.0021,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9958,0.0003,0.0005,0.0019</t>
-  </si>
-  <si>
-    <t>0.9984,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0003,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9960,0.0020,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9881,0.0096,0.0022,0.0017</t>
-  </si>
-  <si>
-    <t>0.9982,0.0007,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9963,0.0003,0.0002,0.0022</t>
-  </si>
-  <si>
-    <t>0.9293,0.0132,0.0540,0.0033</t>
-  </si>
-  <si>
-    <t>0.1506,0.0119,0.8749,0.0030</t>
-  </si>
-  <si>
-    <t>0.4827,0.0049,0.7588,0.0007</t>
-  </si>
-  <si>
-    <t>0.6014,0.0158,0.5397,0.0041</t>
-  </si>
-  <si>
-    <t>0.9725,0.0093,0.0104,0.0014</t>
-  </si>
-  <si>
-    <t>0.0009,0.9980,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.0015,0.9954,0.0009,0.0018</t>
-  </si>
-  <si>
-    <t>0.0263,0.9731,0.0016,0.0038</t>
-  </si>
-  <si>
-    <t>0.0284,0.9722,0.0017,0.0012</t>
-  </si>
-  <si>
-    <t>0.0039,0.9922,0.0016,0.0005</t>
-  </si>
-  <si>
-    <t>0.8796,0.0131,0.1161,0.0069</t>
-  </si>
-  <si>
-    <t>0.7385,0.0042,0.4376,0.0008</t>
-  </si>
-  <si>
-    <t>0.0069,0.0005,0.9918,0.0002</t>
-  </si>
-  <si>
-    <t>0.0807,0.0113,0.8810,0.0140</t>
-  </si>
-  <si>
-    <t>0.2393,0.0008,0.8848,0.0006</t>
-  </si>
-  <si>
-    <t>0.2943,0.0037,0.8044,0.0063</t>
-  </si>
-  <si>
-    <t>0.0127,0.0059,0.9835,0.0009</t>
-  </si>
-  <si>
-    <t>0.6022,0.5464,0.0017,0.0028</t>
-  </si>
-  <si>
-    <t>0.6556,0.3504,0.0428,0.0013</t>
-  </si>
-  <si>
-    <t>0.0123,0.0160,0.9869,0.0031</t>
-  </si>
-  <si>
-    <t>0.0048,0.9764,0.0207,0.0002</t>
-  </si>
-  <si>
-    <t>0.7982,0.2062,0.0230,0.0077</t>
-  </si>
-  <si>
-    <t>0.7478,0.0877,0.1180,0.0013</t>
-  </si>
-  <si>
-    <t>0.8081,0.2868,0.0006,0.0020</t>
-  </si>
-  <si>
-    <t>0.0156,0.9692,0.0633,0.0006</t>
-  </si>
-  <si>
-    <t>0.0148,0.7560,0.7186,0.0151</t>
-  </si>
-  <si>
-    <t>0.7027,0.0114,0.3407,0.0149</t>
-  </si>
-  <si>
-    <t>0.0080,0.1521,0.9863,0.0007</t>
-  </si>
-  <si>
-    <t>0.2619,0.0047,0.8399,0.0030</t>
-  </si>
-  <si>
-    <t>0.0066,0.0580,0.9823,0.0021</t>
-  </si>
-  <si>
-    <t>0.0044,0.9878,0.0054,0.0006</t>
-  </si>
-  <si>
-    <t>0.1456,0.0076,0.9115,0.0003</t>
-  </si>
-  <si>
-    <t>0.0041,0.9747,0.0012,0.2896</t>
-  </si>
-  <si>
-    <t>0.0123,0.9682,0.0492,0.0308</t>
-  </si>
-  <si>
-    <t>0.0004,0.9958,0.0431,0.0003</t>
-  </si>
-  <si>
-    <t>0.0032,0.9785,0.1532,0.0070</t>
-  </si>
-  <si>
-    <t>0.0030,0.0017,0.9953,0.0008</t>
-  </si>
-  <si>
-    <t>0.0040,0.2710,0.9860,0.0009</t>
-  </si>
-  <si>
-    <t>0.0269,0.0060,0.9714,0.0015</t>
-  </si>
-  <si>
-    <t>0.0069,0.0016,0.9826,0.0049</t>
-  </si>
-  <si>
-    <t>0.0027,0.0571,0.9853,0.0007</t>
-  </si>
-  <si>
-    <t>0.0176,0.0085,0.9743,0.0012</t>
-  </si>
-  <si>
-    <t>0.9807,0.0314,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9947,0.0013,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.9813,0.0145,0.0022,0.0027</t>
-  </si>
-  <si>
-    <t>0.0042,0.1027,0.9901,0.0044</t>
-  </si>
-  <si>
-    <t>0.9945,0.0026,0.0007,0.0009</t>
-  </si>
-  <si>
-    <t>0.9968,0.0020,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9897,0.0150,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.8975,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.0033,0.9923,0.0006</t>
-  </si>
-  <si>
-    <t>0.0137,0.0126,0.9830,0.0013</t>
-  </si>
-  <si>
-    <t>0.0001,0.9881,0.9944,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0003,0.9974,0.0004</t>
-  </si>
-  <si>
-    <t>0.0037,0.9858,0.0136,0.0002</t>
-  </si>
-  <si>
-    <t>0.0063,0.9917,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9157,0.0108,0.1207,0.0046</t>
-  </si>
-  <si>
-    <t>0.8144,0.1147,0.0685,0.0258</t>
-  </si>
-  <si>
-    <t>0.0064,0.0066,0.9855,0.0014</t>
-  </si>
-  <si>
-    <t>0.0026,0.9029,0.9618,0.0011</t>
-  </si>
-  <si>
-    <t>0.0070,0.8534,0.5885,0.0005</t>
-  </si>
-  <si>
-    <t>0.0010,0.9927,0.0940,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.9789,0.6931,0.0006</t>
-  </si>
-  <si>
-    <t>0.0035,0.0011,0.0013,0.9976</t>
-  </si>
-  <si>
-    <t>0.0011,0.0025,0.0002,0.9991</t>
-  </si>
-  <si>
-    <t>0.0082,0.0022,0.0002,0.9964</t>
-  </si>
-  <si>
-    <t>0.0133,0.0071,0.0194,0.9829</t>
-  </si>
-  <si>
-    <t>0.0061,0.0011,0.0022,0.9958</t>
-  </si>
-  <si>
-    <t>0.0102,0.0016,0.0003,0.9964</t>
-  </si>
-  <si>
-    <t>0.0001,0.9903,0.9741,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.6700,0.9927,0.0006</t>
-  </si>
-  <si>
-    <t>0.0104,0.3090,0.8646,0.0025</t>
-  </si>
-  <si>
-    <t>0.0019,0.9196,0.9482,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.9932,0.0542,0.0000</t>
-  </si>
-  <si>
-    <t>0.0076,0.8140,0.8533,0.0007</t>
-  </si>
-  <si>
-    <t>0.9971,0.0015,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9954,0.0027,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9748,0.0222,0.0043,0.0033</t>
-  </si>
-  <si>
-    <t>0.9906,0.0048,0.0011,0.0017</t>
-  </si>
-  <si>
-    <t>0.9835,0.0112,0.0014,0.0019</t>
-  </si>
-  <si>
-    <t>0.9974,0.0008,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9958,0.0013,0.0004,0.0012</t>
-  </si>
-  <si>
-    <t>0.9858,0.0102,0.0028,0.0014</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9935,0.0008,0.0010,0.0020</t>
-  </si>
-  <si>
-    <t>0.9966,0.0006,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0001,0.0000,0.0010</t>
-  </si>
-  <si>
-    <t>0.9968,0.0002,0.0000,0.0024</t>
-  </si>
-  <si>
-    <t>0.9976,0.0009,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9889,0.0030,0.0020,0.0031</t>
-  </si>
-  <si>
-    <t>0.9955,0.0010,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.0006,0.0011,0.9969,0.0029</t>
-  </si>
-  <si>
-    <t>0.0944,0.0241,0.9037,0.0023</t>
-  </si>
-  <si>
-    <t>0.9669,0.0048,0.0140,0.0047</t>
-  </si>
-  <si>
-    <t>0.0056,0.0011,0.9891,0.0015</t>
-  </si>
-  <si>
-    <t>0.0417,0.9491,0.0005,0.0093</t>
-  </si>
-  <si>
-    <t>0.0167,0.9782,0.0041,0.0073</t>
-  </si>
-  <si>
-    <t>0.0266,0.9748,0.0025,0.0032</t>
-  </si>
-  <si>
-    <t>0.0747,0.9341,0.0082,0.0030</t>
-  </si>
-  <si>
-    <t>0.0074,0.9890,0.0030,0.0012</t>
-  </si>
-  <si>
-    <t>0.0406,0.9687,0.0028,0.0023</t>
-  </si>
-  <si>
-    <t>0.9806,0.0353,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.5672,0.0547,0.3908,0.0618</t>
-  </si>
-  <si>
-    <t>0.5728,0.0139,0.5966,0.0043</t>
-  </si>
-  <si>
-    <t>0.2262,0.0056,0.8233,0.0023</t>
-  </si>
-  <si>
-    <t>0.4792,0.0495,0.4446,0.0672</t>
-  </si>
-  <si>
-    <t>0.0209,0.0288,0.0153,0.9760</t>
-  </si>
-  <si>
-    <t>0.0003,0.9971,0.0311,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9960,0.0416,0.0044</t>
-  </si>
-  <si>
-    <t>0.0004,0.9977,0.0016,0.0040</t>
-  </si>
-  <si>
-    <t>0.0004,0.9868,0.9523,0.0001</t>
-  </si>
-  <si>
-    <t>0.0142,0.9775,0.0183,0.0006</t>
-  </si>
-  <si>
-    <t>0.8587,0.1792,0.0125,0.0012</t>
-  </si>
-  <si>
-    <t>0.8099,0.2239,0.0102,0.0064</t>
-  </si>
-  <si>
-    <t>0.9933,0.0033,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.9917,0.0008,0.0013,0.0034</t>
-  </si>
-  <si>
-    <t>0.9968,0.0002,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.9834,0.0060,0.0030,0.0043</t>
-  </si>
-  <si>
-    <t>0.9936,0.0011,0.0005,0.0021</t>
-  </si>
-  <si>
-    <t>0.9983,0.0004,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9889,0.0021,0.0013,0.0034</t>
-  </si>
-  <si>
-    <t>0.9680,0.0165,0.0097,0.0042</t>
-  </si>
-  <si>
-    <t>0.0021,0.8649,0.9805,0.0005</t>
-  </si>
-  <si>
-    <t>0.0324,0.3102,0.8468,0.0015</t>
-  </si>
-  <si>
-    <t>0.0096,0.0593,0.9458,0.0002</t>
-  </si>
-  <si>
-    <t>0.0261,0.0206,0.9687,0.0009</t>
-  </si>
-  <si>
-    <t>0.9931,0.0010,0.0019,0.0008</t>
-  </si>
-  <si>
-    <t>0.8145,0.0347,0.1445,0.0122</t>
-  </si>
-  <si>
-    <t>0.0983,0.0024,0.9470,0.0005</t>
-  </si>
-  <si>
-    <t>0.8691,0.0261,0.1009,0.0114</t>
-  </si>
-  <si>
-    <t>0.0119,0.0013,0.0008,0.9952</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0003,0.9996</t>
-  </si>
-  <si>
-    <t>0.0024,0.0019,0.0026,0.9972</t>
-  </si>
-  <si>
-    <t>0.0053,0.0002,0.0009,0.9972</t>
-  </si>
-  <si>
-    <t>0.0034,0.9144,0.7596,0.0016</t>
-  </si>
-  <si>
-    <t>0.9550,0.0207,0.0245,0.0026</t>
-  </si>
-  <si>
-    <t>0.2897,0.7963,0.0026,0.0016</t>
-  </si>
-  <si>
-    <t>0.9940,0.0009,0.0004,0.0025</t>
-  </si>
-  <si>
-    <t>0.2444,0.7131,0.0255,0.0062</t>
-  </si>
-  <si>
-    <t>0.9837,0.0036,0.0020,0.0046</t>
-  </si>
-  <si>
-    <t>0.8980,0.0113,0.0115,0.0930</t>
-  </si>
-  <si>
-    <t>0.9928,0.0046,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.0321,0.2605,0.8605,0.0980</t>
-  </si>
-  <si>
-    <t>0.8465,0.0038,0.0053,0.2209</t>
-  </si>
-  <si>
-    <t>0.9687,0.0045,0.0060,0.0139</t>
-  </si>
-  <si>
-    <t>0.3282,0.6396,0.0029,0.0185</t>
-  </si>
-  <si>
-    <t>0.9688,0.0147,0.0041,0.0054</t>
-  </si>
-  <si>
-    <t>0.9859,0.0024,0.0069,0.0008</t>
-  </si>
-  <si>
-    <t>0.1366,0.8637,0.0346,0.0124</t>
-  </si>
-  <si>
-    <t>0.9857,0.0051,0.0039,0.0008</t>
-  </si>
-  <si>
-    <t>0.9779,0.0089,0.0074,0.0008</t>
-  </si>
-  <si>
-    <t>0.9919,0.0023,0.0038,0.0006</t>
-  </si>
-  <si>
-    <t>0.9936,0.0019,0.0008,0.0014</t>
-  </si>
-  <si>
-    <t>0.9889,0.0067,0.0027,0.0015</t>
-  </si>
-  <si>
-    <t>0.9951,0.0014,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.9795,0.0052,0.0084,0.0022</t>
-  </si>
-  <si>
-    <t>0.9722,0.0323,0.0058,0.0015</t>
-  </si>
-  <si>
-    <t>0.9946,0.0006,0.0003,0.0027</t>
-  </si>
-  <si>
-    <t>0.9972,0.0005,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.6655,0.4250,0.0069,0.0065</t>
-  </si>
-  <si>
-    <t>0.3838,0.7531,0.0043,0.0008</t>
-  </si>
-  <si>
-    <t>0.6541,0.4604,0.0033,0.0040</t>
-  </si>
-  <si>
-    <t>0.2070,0.3826,0.7969,0.0112</t>
-  </si>
-  <si>
-    <t>0.9813,0.0374,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9687,0.0296,0.0063,0.0020</t>
-  </si>
-  <si>
-    <t>0.9831,0.0145,0.0040,0.0011</t>
-  </si>
-  <si>
-    <t>0.8852,0.1753,0.0050,0.0026</t>
-  </si>
-  <si>
-    <t>0.0021,0.0703,0.9918,0.0032</t>
-  </si>
-  <si>
-    <t>0.9830,0.0240,0.0028,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.0054,0.9951,0.0010</t>
-  </si>
-  <si>
-    <t>0.0125,0.0456,0.9807,0.0046</t>
-  </si>
-  <si>
-    <t>0.0061,0.0128,0.9754,0.0056</t>
-  </si>
-  <si>
-    <t>0.0013,0.0004,0.9949,0.0022</t>
-  </si>
-  <si>
-    <t>0.0018,0.0020,0.9935,0.0013</t>
-  </si>
-  <si>
-    <t>0.0215,0.0060,0.9775,0.0013</t>
-  </si>
-  <si>
-    <t>0.0026,0.0010,0.9942,0.0014</t>
-  </si>
-  <si>
-    <t>0.1173,0.0548,0.8360,0.0061</t>
-  </si>
-  <si>
-    <t>0.4464,0.0031,0.7126,0.0014</t>
-  </si>
-  <si>
-    <t>0.6693,0.0896,0.2641,0.0145</t>
-  </si>
-  <si>
-    <t>0.0628,0.3163,0.5198,0.0011</t>
-  </si>
-  <si>
-    <t>0.0490,0.1917,0.7147,0.0012</t>
-  </si>
-  <si>
-    <t>0.6850,0.0223,0.3792,0.0039</t>
-  </si>
-  <si>
-    <t>0.6802,0.0313,0.3431,0.0076</t>
-  </si>
-  <si>
-    <t>0.7053,0.0353,0.2610,0.0094</t>
-  </si>
-  <si>
-    <t>0.8111,0.3356,0.0058,0.0008</t>
-  </si>
-  <si>
-    <t>0.9511,0.0947,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.9771,0.0302,0.0018,0.0008</t>
-  </si>
-  <si>
-    <t>0.9864,0.0181,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.4460,0.6882,0.0029,0.0042</t>
-  </si>
-  <si>
-    <t>0.8841,0.0269,0.0964,0.0036</t>
-  </si>
-  <si>
-    <t>0.9229,0.0015,0.1185,0.0020</t>
-  </si>
-  <si>
-    <t>0.9417,0.0275,0.0056,0.0118</t>
-  </si>
-  <si>
-    <t>0.7306,0.0057,0.4275,0.0024</t>
-  </si>
-  <si>
-    <t>0.4722,0.0226,0.5620,0.0059</t>
-  </si>
-  <si>
-    <t>0.0010,0.0021,0.9935,0.0044</t>
-  </si>
-  <si>
-    <t>0.0184,0.0218,0.9684,0.0032</t>
-  </si>
-  <si>
-    <t>0.0012,0.0083,0.9966,0.0004</t>
-  </si>
-  <si>
-    <t>0.1708,0.0078,0.8244,0.0075</t>
-  </si>
-  <si>
-    <t>0.0113,0.0040,0.9836,0.0015</t>
-  </si>
-  <si>
-    <t>0.9959,0.0004,0.0002,0.0021</t>
-  </si>
-  <si>
-    <t>0.9925,0.0021,0.0022,0.0008</t>
-  </si>
-  <si>
-    <t>0.9943,0.0036,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9906,0.0090,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9882,0.0092,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.9944,0.0026,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.9962,0.0008,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9969,0.0006,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.0093,0.1222,0.9839,0.0028</t>
-  </si>
-  <si>
-    <t>0.3376,0.0672,0.6566,0.0035</t>
-  </si>
-  <si>
-    <t>0.9312,0.0199,0.0405,0.0058</t>
-  </si>
-  <si>
-    <t>0.0015,0.0017,0.9943,0.0017</t>
-  </si>
-  <si>
-    <t>0.0003,0.0008,0.9980,0.0006</t>
-  </si>
-  <si>
-    <t>0.0265,0.0979,0.9405,0.0027</t>
-  </si>
-  <si>
-    <t>0.0021,0.0023,0.9974,0.0003</t>
-  </si>
-  <si>
-    <t>0.0375,0.0908,0.8695,0.0083</t>
-  </si>
-  <si>
-    <t>0.0011,0.0022,0.9966,0.0006</t>
-  </si>
-  <si>
-    <t>0.0045,0.0054,0.9879,0.0010</t>
-  </si>
-  <si>
-    <t>0.0102,0.0223,0.9560,0.0054</t>
-  </si>
-  <si>
-    <t>0.8296,0.0318,0.1613,0.0062</t>
-  </si>
-  <si>
-    <t>0.8862,0.0008,0.2065,0.0013</t>
-  </si>
-  <si>
-    <t>0.9913,0.0011,0.0035,0.0010</t>
-  </si>
-  <si>
-    <t>0.9952,0.0013,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.9830,0.0245,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.9955,0.0017,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9918,0.0044,0.0017,0.0006</t>
-  </si>
-  <si>
-    <t>0.9878,0.0071,0.0011,0.0026</t>
-  </si>
-  <si>
-    <t>0.9831,0.0332,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9960,0.0026,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9949,0.0013,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.0266,0.0251,0.9634,0.0011</t>
-  </si>
-  <si>
-    <t>0.0019,0.0631,0.9913,0.0003</t>
-  </si>
-  <si>
-    <t>0.0056,0.1062,0.9672,0.0030</t>
-  </si>
-  <si>
-    <t>0.0079,0.3934,0.7836,0.0055</t>
-  </si>
-  <si>
-    <t>0.1198,0.0135,0.9347,0.0020</t>
-  </si>
-  <si>
-    <t>0.4013,0.0222,0.5373,0.0785</t>
-  </si>
-  <si>
-    <t>0.0206,0.0427,0.9195,0.0263</t>
-  </si>
-  <si>
-    <t>0.0707,0.0017,0.9056,0.0066</t>
-  </si>
-  <si>
-    <t>0.6112,0.0023,0.0029,0.6366</t>
-  </si>
-  <si>
-    <t>0.0037,0.2098,0.0008,0.9846</t>
-  </si>
-  <si>
-    <t>0.1069,0.0010,0.0016,0.9685</t>
-  </si>
-  <si>
-    <t>0.0063,0.0001,0.0001,0.9982</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.0012,0.9989</t>
-  </si>
-  <si>
-    <t>0.9417,0.0049,0.0096,0.0335</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9857,0.0030,0.0012,0.0043</t>
+  </si>
+  <si>
+    <t>0.0077,0.0009,0.0006,0.9972</t>
+  </si>
+  <si>
+    <t>0.9224,0.0010,0.0019,0.1134</t>
+  </si>
+  <si>
+    <t>0.0955,0.0058,0.0026,0.9460</t>
+  </si>
+  <si>
+    <t>0.9968,0.0019,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9927,0.0004,0.0001,0.0058</t>
+  </si>
+  <si>
+    <t>0.9938,0.0077,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9963,0.0007,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9904,0.0072,0.0012,0.0016</t>
+  </si>
+  <si>
+    <t>0.9983,0.0008,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9974,0.0012,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9447,0.0043,0.0621,0.0015</t>
+  </si>
+  <si>
+    <t>0.1343,0.0179,0.8735,0.0118</t>
+  </si>
+  <si>
+    <t>0.1182,0.0328,0.8803,0.0026</t>
+  </si>
+  <si>
+    <t>0.0880,0.0084,0.8959,0.0041</t>
+  </si>
+  <si>
+    <t>0.8615,0.0134,0.1596,0.0020</t>
+  </si>
+  <si>
+    <t>0.0014,0.9969,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.0030,0.9953,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.0300,0.9701,0.0021,0.0025</t>
+  </si>
+  <si>
+    <t>0.1714,0.9009,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.0050,0.9932,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.7002,0.0055,0.3913,0.0026</t>
+  </si>
+  <si>
+    <t>0.8109,0.0041,0.2572,0.0030</t>
+  </si>
+  <si>
+    <t>0.0526,0.0038,0.9551,0.0013</t>
+  </si>
+  <si>
+    <t>0.0083,0.0015,0.9834,0.0010</t>
+  </si>
+  <si>
+    <t>0.0783,0.0048,0.9595,0.0014</t>
+  </si>
+  <si>
+    <t>0.0619,0.0069,0.9376,0.0051</t>
+  </si>
+  <si>
+    <t>0.0024,0.0026,0.9935,0.0037</t>
+  </si>
+  <si>
+    <t>0.9322,0.0479,0.0141,0.0005</t>
+  </si>
+  <si>
+    <t>0.2932,0.6281,0.0853,0.0160</t>
+  </si>
+  <si>
+    <t>0.0027,0.0095,0.9944,0.0012</t>
+  </si>
+  <si>
+    <t>0.0035,0.9853,0.0296,0.0004</t>
+  </si>
+  <si>
+    <t>0.8448,0.1279,0.0374,0.0207</t>
+  </si>
+  <si>
+    <t>0.9231,0.0226,0.0526,0.0035</t>
+  </si>
+  <si>
+    <t>0.9799,0.0219,0.0035,0.0004</t>
+  </si>
+  <si>
+    <t>0.2067,0.7838,0.1205,0.0035</t>
+  </si>
+  <si>
+    <t>0.0117,0.8540,0.1947,0.0285</t>
+  </si>
+  <si>
+    <t>0.5705,0.0077,0.5185,0.0068</t>
+  </si>
+  <si>
+    <t>0.0123,0.0066,0.9837,0.0010</t>
+  </si>
+  <si>
+    <t>0.2268,0.0071,0.7935,0.0138</t>
+  </si>
+  <si>
+    <t>0.0156,0.1006,0.9390,0.0005</t>
+  </si>
+  <si>
+    <t>0.0024,0.9909,0.0028,0.0010</t>
+  </si>
+  <si>
+    <t>0.4364,0.0188,0.6726,0.0044</t>
+  </si>
+  <si>
+    <t>0.0004,0.9927,0.0005,0.2808</t>
+  </si>
+  <si>
+    <t>0.0018,0.9848,0.0207,0.0231</t>
+  </si>
+  <si>
+    <t>0.0003,0.9968,0.0244,0.0003</t>
+  </si>
+  <si>
+    <t>0.0019,0.9846,0.2151,0.0033</t>
+  </si>
+  <si>
+    <t>0.0520,0.0040,0.9366,0.0038</t>
+  </si>
+  <si>
+    <t>0.0058,0.5711,0.9627,0.0018</t>
+  </si>
+  <si>
+    <t>0.0701,0.0094,0.9368,0.0038</t>
+  </si>
+  <si>
+    <t>0.0037,0.0022,0.9935,0.0009</t>
+  </si>
+  <si>
+    <t>0.0012,0.0128,0.9935,0.0001</t>
+  </si>
+  <si>
+    <t>0.0314,0.0180,0.9461,0.0034</t>
+  </si>
+  <si>
+    <t>0.9427,0.0718,0.0014,0.0027</t>
+  </si>
+  <si>
+    <t>0.9956,0.0027,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9969,0.0007,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.0119,0.0323,0.9902,0.0012</t>
+  </si>
+  <si>
+    <t>0.9938,0.0017,0.0005,0.0018</t>
+  </si>
+  <si>
+    <t>0.9981,0.0006,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9923,0.0084,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.0030,0.8446,0.9776,0.0008</t>
+  </si>
+  <si>
+    <t>0.0099,0.0264,0.9852,0.0021</t>
+  </si>
+  <si>
+    <t>0.0080,0.0102,0.9887,0.0023</t>
+  </si>
+  <si>
+    <t>0.0002,0.9428,0.9945,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0003,0.9953,0.0014</t>
+  </si>
+  <si>
+    <t>0.0155,0.9700,0.0122,0.0004</t>
+  </si>
+  <si>
+    <t>0.0073,0.9908,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.9444,0.0138,0.0422,0.0056</t>
+  </si>
+  <si>
+    <t>0.2763,0.0457,0.7814,0.0214</t>
+  </si>
+  <si>
+    <t>0.0201,0.0120,0.9713,0.0028</t>
+  </si>
+  <si>
+    <t>0.0006,0.9850,0.7570,0.0002</t>
+  </si>
+  <si>
+    <t>0.0043,0.8788,0.7736,0.0005</t>
+  </si>
+  <si>
+    <t>0.0012,0.9944,0.0248,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.9548,0.6372,0.0009</t>
+  </si>
+  <si>
+    <t>0.0046,0.0008,0.0108,0.9927</t>
+  </si>
+  <si>
+    <t>0.0008,0.0036,0.0005,0.9989</t>
+  </si>
+  <si>
+    <t>0.0115,0.0020,0.0015,0.9941</t>
+  </si>
+  <si>
+    <t>0.0258,0.0331,0.0024,0.9813</t>
+  </si>
+  <si>
+    <t>0.0301,0.0026,0.0024,0.9864</t>
+  </si>
+  <si>
+    <t>0.0048,0.0101,0.0004,0.9968</t>
+  </si>
+  <si>
+    <t>0.0002,0.9867,0.9747,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.8814,0.9933,0.0002</t>
+  </si>
+  <si>
+    <t>0.0079,0.8544,0.3738,0.0008</t>
+  </si>
+  <si>
+    <t>0.0020,0.8939,0.9786,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.9936,0.2438,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.9523,0.8761,0.0005</t>
+  </si>
+  <si>
+    <t>0.9941,0.0026,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9739,0.0324,0.0033,0.0009</t>
+  </si>
+  <si>
+    <t>0.9913,0.0126,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9939,0.0020,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9781,0.0302,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9939,0.0037,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9853,0.0102,0.0036,0.0028</t>
+  </si>
+  <si>
+    <t>0.9872,0.0059,0.0032,0.0019</t>
+  </si>
+  <si>
+    <t>0.9956,0.0003,0.0010,0.0012</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9841,0.0110,0.0028,0.0034</t>
+  </si>
+  <si>
+    <t>0.9936,0.0019,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.9946,0.0007,0.0007,0.0018</t>
+  </si>
+  <si>
+    <t>0.0018,0.0008,0.9951,0.0032</t>
+  </si>
+  <si>
+    <t>0.0186,0.0065,0.9787,0.0006</t>
+  </si>
+  <si>
+    <t>0.9867,0.0012,0.0072,0.0016</t>
+  </si>
+  <si>
+    <t>0.0197,0.0013,0.9818,0.0007</t>
+  </si>
+  <si>
+    <t>0.0055,0.9911,0.0024,0.0017</t>
+  </si>
+  <si>
+    <t>0.0070,0.9890,0.0024,0.0028</t>
+  </si>
+  <si>
+    <t>0.0505,0.9556,0.0031,0.0058</t>
+  </si>
+  <si>
+    <t>0.0100,0.9849,0.0081,0.0016</t>
+  </si>
+  <si>
+    <t>0.0018,0.9960,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.0147,0.9792,0.0045,0.0055</t>
+  </si>
+  <si>
+    <t>0.8947,0.1813,0.0019,0.0009</t>
+  </si>
+  <si>
+    <t>0.3357,0.0746,0.6169,0.0347</t>
+  </si>
+  <si>
+    <t>0.2641,0.0071,0.8229,0.0043</t>
+  </si>
+  <si>
+    <t>0.5036,0.0559,0.4599,0.0063</t>
+  </si>
+  <si>
+    <t>0.4710,0.0384,0.6214,0.0069</t>
+  </si>
+  <si>
+    <t>0.0067,0.6058,0.0107,0.8566</t>
+  </si>
+  <si>
+    <t>0.0004,0.9953,0.0346,0.0028</t>
+  </si>
+  <si>
+    <t>0.0013,0.9926,0.0047,0.0027</t>
+  </si>
+  <si>
+    <t>0.0018,0.9910,0.0047,0.0047</t>
+  </si>
+  <si>
+    <t>0.0005,0.9810,0.8027,0.0005</t>
+  </si>
+  <si>
+    <t>0.0017,0.9966,0.0020,0.0007</t>
+  </si>
+  <si>
+    <t>0.8647,0.1886,0.0030,0.0021</t>
+  </si>
+  <si>
+    <t>0.8884,0.1332,0.0193,0.0044</t>
+  </si>
+  <si>
+    <t>0.9970,0.0013,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9948,0.0017,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9943,0.0020,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.9885,0.0049,0.0030,0.0010</t>
+  </si>
+  <si>
+    <t>0.9956,0.0006,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.9964,0.0012,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9860,0.0065,0.0014,0.0022</t>
+  </si>
+  <si>
+    <t>0.9880,0.0021,0.0015,0.0057</t>
+  </si>
+  <si>
+    <t>0.0011,0.5079,0.9900,0.0005</t>
+  </si>
+  <si>
+    <t>0.0089,0.1845,0.9599,0.0010</t>
+  </si>
+  <si>
+    <t>0.0215,0.0693,0.9385,0.0005</t>
+  </si>
+  <si>
+    <t>0.0219,0.0259,0.9738,0.0003</t>
+  </si>
+  <si>
+    <t>0.7198,0.2018,0.0260,0.0579</t>
+  </si>
+  <si>
+    <t>0.8501,0.0062,0.1748,0.0101</t>
+  </si>
+  <si>
+    <t>0.0315,0.0095,0.9750,0.0027</t>
+  </si>
+  <si>
+    <t>0.8515,0.0230,0.1430,0.0032</t>
+  </si>
+  <si>
+    <t>0.0232,0.0017,0.0012,0.9894</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0019,0.0104,0.0021,0.9967</t>
+  </si>
+  <si>
+    <t>0.0067,0.0001,0.0011,0.9964</t>
+  </si>
+  <si>
+    <t>0.0116,0.9319,0.2479,0.0014</t>
+  </si>
+  <si>
+    <t>0.9783,0.0054,0.0090,0.0025</t>
+  </si>
+  <si>
+    <t>0.1078,0.9113,0.0018,0.0074</t>
+  </si>
+  <si>
+    <t>0.9813,0.0055,0.0022,0.0067</t>
+  </si>
+  <si>
+    <t>0.2508,0.7900,0.0119,0.0081</t>
+  </si>
+  <si>
+    <t>0.9926,0.0025,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.9498,0.0069,0.0023,0.0312</t>
+  </si>
+  <si>
+    <t>0.9954,0.0013,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.0037,0.0746,0.8324,0.2582</t>
+  </si>
+  <si>
+    <t>0.9076,0.0003,0.0008,0.1943</t>
+  </si>
+  <si>
+    <t>0.9877,0.0008,0.0000,0.0050</t>
+  </si>
+  <si>
+    <t>0.6484,0.3897,0.0049,0.0079</t>
+  </si>
+  <si>
+    <t>0.9935,0.0025,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9739,0.0124,0.0046,0.0030</t>
+  </si>
+  <si>
+    <t>0.4913,0.4892,0.0243,0.0064</t>
+  </si>
+  <si>
+    <t>0.9412,0.0094,0.0601,0.0010</t>
+  </si>
+  <si>
+    <t>0.9785,0.0092,0.0067,0.0005</t>
+  </si>
+  <si>
+    <t>0.9972,0.0004,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9895,0.0015,0.0006,0.0049</t>
+  </si>
+  <si>
+    <t>0.9938,0.0016,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.9939,0.0013,0.0009,0.0020</t>
+  </si>
+  <si>
+    <t>0.9914,0.0021,0.0015,0.0022</t>
+  </si>
+  <si>
+    <t>0.9756,0.0293,0.0033,0.0011</t>
+  </si>
+  <si>
+    <t>0.9951,0.0020,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9898,0.0007,0.0024,0.0029</t>
+  </si>
+  <si>
+    <t>0.5402,0.5396,0.0124,0.0052</t>
+  </si>
+  <si>
+    <t>0.1824,0.8531,0.0053,0.0020</t>
+  </si>
+  <si>
+    <t>0.0826,0.9378,0.0026,0.0033</t>
+  </si>
+  <si>
+    <t>0.0404,0.6658,0.9093,0.0050</t>
+  </si>
+  <si>
+    <t>0.9798,0.0216,0.0037,0.0009</t>
+  </si>
+  <si>
+    <t>0.9539,0.0623,0.0036,0.0022</t>
+  </si>
+  <si>
+    <t>0.9940,0.0045,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9836,0.0092,0.0017,0.0031</t>
+  </si>
+  <si>
+    <t>0.0041,0.1129,0.9916,0.0028</t>
+  </si>
+  <si>
+    <t>0.9885,0.0101,0.0037,0.0002</t>
+  </si>
+  <si>
+    <t>0.0025,0.0097,0.9891,0.0005</t>
+  </si>
+  <si>
+    <t>0.0304,0.0146,0.9503,0.0119</t>
+  </si>
+  <si>
+    <t>0.0027,0.0058,0.9926,0.0027</t>
+  </si>
+  <si>
+    <t>0.0006,0.0008,0.9969,0.0018</t>
+  </si>
+  <si>
+    <t>0.0045,0.0032,0.9893,0.0008</t>
+  </si>
+  <si>
+    <t>0.0029,0.0061,0.9910,0.0013</t>
+  </si>
+  <si>
+    <t>0.0098,0.0035,0.9896,0.0004</t>
+  </si>
+  <si>
+    <t>0.2151,0.0215,0.8044,0.0021</t>
+  </si>
+  <si>
+    <t>0.1214,0.0140,0.9171,0.0035</t>
+  </si>
+  <si>
+    <t>0.0623,0.0602,0.8525,0.0206</t>
+  </si>
+  <si>
+    <t>0.0876,0.3155,0.5258,0.0063</t>
+  </si>
+  <si>
+    <t>0.1513,0.3059,0.3861,0.0021</t>
+  </si>
+  <si>
+    <t>0.1169,0.0930,0.6629,0.0015</t>
+  </si>
+  <si>
+    <t>0.6875,0.0749,0.2752,0.0291</t>
+  </si>
+  <si>
+    <t>0.0587,0.0178,0.9130,0.0028</t>
+  </si>
+  <si>
+    <t>0.7143,0.4516,0.0029,0.0004</t>
+  </si>
+  <si>
+    <t>0.9230,0.1654,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9888,0.0183,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9965,0.0024,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.7231,0.3554,0.0037,0.0074</t>
+  </si>
+  <si>
+    <t>0.7052,0.0588,0.2178,0.0028</t>
+  </si>
+  <si>
+    <t>0.9694,0.0006,0.0433,0.0008</t>
+  </si>
+  <si>
+    <t>0.9172,0.0080,0.0105,0.0378</t>
+  </si>
+  <si>
+    <t>0.9306,0.0087,0.0550,0.0058</t>
+  </si>
+  <si>
+    <t>0.6070,0.0139,0.4290,0.0061</t>
+  </si>
+  <si>
+    <t>0.0022,0.0019,0.9888,0.0064</t>
+  </si>
+  <si>
+    <t>0.0210,0.0181,0.9596,0.0023</t>
+  </si>
+  <si>
+    <t>0.0134,0.0075,0.9863,0.0005</t>
+  </si>
+  <si>
+    <t>0.0641,0.0562,0.8347,0.0024</t>
+  </si>
+  <si>
+    <t>0.0135,0.1979,0.9383,0.0042</t>
+  </si>
+  <si>
+    <t>0.9932,0.0033,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.9859,0.0069,0.0023,0.0027</t>
+  </si>
+  <si>
+    <t>0.9926,0.0030,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.9734,0.0282,0.0047,0.0007</t>
+  </si>
+  <si>
+    <t>0.9884,0.0057,0.0006,0.0027</t>
+  </si>
+  <si>
+    <t>0.9873,0.0058,0.0012,0.0029</t>
+  </si>
+  <si>
+    <t>0.9978,0.0007,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9947,0.0014,0.0003,0.0017</t>
+  </si>
+  <si>
+    <t>0.0098,0.0368,0.9729,0.0159</t>
+  </si>
+  <si>
+    <t>0.0114,0.6498,0.6471,0.0076</t>
+  </si>
+  <si>
+    <t>0.8910,0.0018,0.1436,0.0006</t>
+  </si>
+  <si>
+    <t>0.0017,0.0123,0.9921,0.0011</t>
+  </si>
+  <si>
+    <t>0.0073,0.0044,0.9828,0.0016</t>
+  </si>
+  <si>
+    <t>0.0094,0.0345,0.9763,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.0020,0.9957,0.0010</t>
+  </si>
+  <si>
+    <t>0.0331,0.0237,0.9445,0.0018</t>
+  </si>
+  <si>
+    <t>0.0001,0.0012,0.9993,0.0003</t>
+  </si>
+  <si>
+    <t>0.0016,0.0034,0.9935,0.0007</t>
+  </si>
+  <si>
+    <t>0.0077,0.0262,0.9433,0.0142</t>
+  </si>
+  <si>
+    <t>0.9586,0.0042,0.0415,0.0021</t>
+  </si>
+  <si>
+    <t>0.9735,0.0002,0.0392,0.0005</t>
+  </si>
+  <si>
+    <t>0.9779,0.0021,0.0119,0.0035</t>
+  </si>
+  <si>
+    <t>0.9936,0.0014,0.0007,0.0016</t>
+  </si>
+  <si>
+    <t>0.9890,0.0053,0.0021,0.0021</t>
+  </si>
+  <si>
+    <t>0.9974,0.0012,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9811,0.0198,0.0030,0.0017</t>
+  </si>
+  <si>
+    <t>0.9977,0.0004,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9594,0.0634,0.0032,0.0008</t>
+  </si>
+  <si>
+    <t>0.9919,0.0048,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.9935,0.0013,0.0011,0.0026</t>
+  </si>
+  <si>
+    <t>0.0069,0.0076,0.9773,0.0007</t>
+  </si>
+  <si>
+    <t>0.0007,0.0312,0.9937,0.0013</t>
+  </si>
+  <si>
+    <t>0.0067,0.1027,0.9814,0.0013</t>
+  </si>
+  <si>
+    <t>0.0037,0.0031,0.9796,0.0021</t>
+  </si>
+  <si>
+    <t>0.0156,0.0025,0.9869,0.0004</t>
+  </si>
+  <si>
+    <t>0.0258,0.0111,0.8799,0.1538</t>
+  </si>
+  <si>
+    <t>0.0640,0.0082,0.9272,0.0030</t>
+  </si>
+  <si>
+    <t>0.0338,0.0027,0.9619,0.0024</t>
+  </si>
+  <si>
+    <t>0.8730,0.0063,0.0022,0.1592</t>
+  </si>
+  <si>
+    <t>0.0316,0.0253,0.0073,0.9794</t>
+  </si>
+  <si>
+    <t>0.0393,0.0026,0.0043,0.9828</t>
+  </si>
+  <si>
+    <t>0.0026,0.0003,0.0003,0.9987</t>
+  </si>
+  <si>
+    <t>0.0009,0.0003,0.0002,0.9995</t>
+  </si>
+  <si>
+    <t>0.5509,0.0068,0.0070,0.6260</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1985,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2013,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2069,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2083,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2097,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2125,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2139,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2153,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2167,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2195,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2209,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2223,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2237,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2251,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2265,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2279,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2293,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2307,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2335,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2349,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2374,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2388,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2419,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2433,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2447,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2461,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2486,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2500,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2517,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2531,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2545,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2559,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2587,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2601,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2615,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2629,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2643,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2654,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2671,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2699,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2741,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2755,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2783,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2797,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2811,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2825,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2839,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2853,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2867,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2881,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2895,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2923,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2934,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2951,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2965,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2979,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2993,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3007,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3021,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3035,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3049,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3063,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3077,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3091,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3105,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3119,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3130,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3147,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3161,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3175,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3329,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3343,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3371,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3385,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3399,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3413,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3427,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3441,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3455,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3483,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3497,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3511,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3553,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3564,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3581,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3592,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3606,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3620,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3637,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3651,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3665,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3679,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3693,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3707,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3721,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3763,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3791,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3805,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3847,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3861,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3875,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3889,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3903,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3917,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3931,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3959,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3973,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3987,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +4001,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4012,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4043,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4071,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4085,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4099,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4127,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4141,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4166,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4208,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4362,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4379,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4390,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4404,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4421,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4435,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4449,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4463,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4491,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4547,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4603,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4617,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4628,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4645,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4656,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4670,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4687,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4698,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4715,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4729,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4743,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4757,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4768,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4785,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4813,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4827,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4838,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4855,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4869,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4883,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4897,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4911,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4953,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4967,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4995,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5009,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5023,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5048,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5107,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5121,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5135,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5149,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5163,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5177,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5261,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5275,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5289,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5303,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5317,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5331,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5373,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5387,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5401,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5415,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5429,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5443,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5454,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5471,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5485,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5499,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5513,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5524,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
